--- a/microbit-program/autumn-2026/quiz/kahoot-import/week-03.xlsx
+++ b/microbit-program/autumn-2026/quiz/kahoot-import/week-03.xlsx
@@ -413,17 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -465,27 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Which block gives you a surprise number?</t>
+          <t>Which block plays a built-in tune like "Ba Ding"?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>start melody</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>show icon</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>pick random</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>show number</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pause</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>clear screen</t>
+          <t>radio send number</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,166 +489,562 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Which sensor notices when you SHAKE the micro:bit?</t>
+          <t>Two micro:bits can only hear each other over radio if they share the same…</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Accelerometer</t>
+          <t>colour</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thermometer</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Light sensor</t>
+          <t>group number</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>button</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A dice should show numbers…</t>
+          <t>Which block sends a message through the air to another micro:bit?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 to 6</t>
+          <t>show string</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0 to 9</t>
+          <t>radio send number</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1 to 10</t>
+          <t>pause</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0 to 5</t>
+          <t>show leds</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>What do you touch to use the Love Meter?</t>
+          <t>Which block runs when a message ARRIVES from another micro:bit?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pin 0 and GND</t>
+          <t>on start</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The USB port</t>
+          <t>on button A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The buttons</t>
+          <t>on shake</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The LEDs</t>
+          <t>on radio received</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>🎉 How many sides does a normal dice have?</t>
+          <t>The Fortune Teller picks its answer with pick random and…</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>play tone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>if / else</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>show number</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>🎉 What is the fastest land animal?</t>
+          <t>In the Love Meter, you complete a circuit by holding…</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>the USB port</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>button A and B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>two LEDs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>pin 0 and GND</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A switch the ball closes is read with which block?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>digital read pin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>play tone</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>show icon</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>set volume</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>`set pull pin P0 up` makes the pin read 1 when open — what when closed?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>still 1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>How often does a `forever` loop check the switch?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>once at the start</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>only when you press A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>all the time, over and over</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Adding points inside a forever loop while you HOLD a switch makes the score…</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>stay at 0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>shoot up way too fast</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>count down</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>The `wasClosed` flag makes sure one hit scores…</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>a hundred times</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>only once</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>forever</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A machine that remembers "left lane first, then right = BONUS" is using…</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>state (it remembers)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>a melody</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>a random number</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>🎮 In games, what does "noob" mean?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A boss</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A prize</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A new player</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A map</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>🐛 A "glitch" or bug in a game is…</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>a mistake in the code</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>a new level</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>a controller</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>a snack</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>🎉 What does "GG" mean at the end of a match?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Get Going</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Great Goal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Go Green</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Good Game</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>🏁 A "speedrun" means finishing a game…</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>with your eyes closed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>as fast as you can</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>backwards</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>on paper</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>🐌 When an online game gets slow and jumpy, players call it…</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>lag</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>loot</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>a combo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>a skin</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>🚀 Which planet is nicknamed the "Red Planet"?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Venus</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jupiter</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Saturn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
